--- a/per-stock/UMC/financials.xlsx
+++ b/per-stock/UMC/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43207208960</v>
+        <v>60423622656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>158166335488</v>
+        <v>2387994112</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.741936</v>
+        <v>38.83871</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.43329</v>
+        <v>29.534416</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1794825</v>
+        <v>0.2509994</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34353795072</v>
+        <v>48560410000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2512046774</v>
+        <v>2509286774</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.2</v>
+        <v>24.08</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D56</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C56</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B56</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B54:E54)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B52:E52)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1180,7 +1648,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2469322400</v>
+        <v>2521458000</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>2525776000</v>
@@ -1200,7 +1668,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2444956600</v>
+        <v>2497092200</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>2487319800</v>
@@ -1220,7 +1688,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>16.35</v>
+        <v>16.55</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>18.7</v>
@@ -1240,7 +1708,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>19</v>
@@ -1944,7 +2412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3292,7 +3760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5192,7 +5660,2331 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>12578524619</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>12588156344</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>12556327419</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>12557000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>12558000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>12578524619</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>12588156344</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>12556327419</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>12557000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>12558000000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>56737158000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>59781672000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>75911382000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>68894116000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>57466946000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>402240778000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>361082121000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>356603947000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>333109545000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>386695151000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>457455296000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>419605823000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>430878014000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>399773985000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>441732308000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>136828894000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>115256071000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>110577892000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>84782174000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>119449720000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>402240778000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>361082121000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>356603947000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>333109545000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>386695151000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>5982459000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>6000846000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>6093587000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5991630000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6339536000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>406700597000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>365824997000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>361060219000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>336871499000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>390604898000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>453865625000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>411197051000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>414817829000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>378471649000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>435232308000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>406736158000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>365912172000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>361200194000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>337045506000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>390828631000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>35561000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>87175000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>139975000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>174007000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>223733000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>406700597000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>365824997000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>361060219000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>336871499000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>390604898000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6056128000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1977084000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>5462138000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5492781000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5481417000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>57503890000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>45328808000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>39264420000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>30019559000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>52138647000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>41466099000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>41466099000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>41466099000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>41466099000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>36727862000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Foreign Currency Translation Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>322108000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-4435016000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-12621178000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-21233142000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>5163151000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Minimum Pension Liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-1873017000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-2122645000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-1319042000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-1553094000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-1770458000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unrealized Gain Loss</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>17588700000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>10420370000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>11738541000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>11339696000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>12018092000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>9803778000</v>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>9803778000</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>207599300000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>184173477000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>181240637000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>166264200000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>197887505000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>9756033000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>18267843000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>9529750000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>9529882000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>9513739000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>125785246000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>125881563000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>125563274000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>125565077000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>125583590000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>125785246000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>125881563000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125563274000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>125565077000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>125583590000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>193195750000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>201362691000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>194195228000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>211098060000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>182133652000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>113584375000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>111835504000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>111919443000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>100705346000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>109260286000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46357560000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>46218398000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>45062149000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>44664652000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>48898946000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>849970000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>866219000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1024785000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1038286000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1051517000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n">
+        <v>1038286000</v>
+      </c>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>13857468000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>14002812000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>6625559000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>8020468000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>8982712000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1795430000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1787375000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>474880000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>456364000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>465220000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>12062038000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>12215437000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>6150679000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>7564104000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>8517492000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>52519377000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>50748075000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>59206950000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46981940000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>50327111000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>5354349000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>5376021000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>5449340000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5381790000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>5699701000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>47165028000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>45372054000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>53757610000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>41600150000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>44627410000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>79611375000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>89527187000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>82275785000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>110392714000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>72873366000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>26843803000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>27103923000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>21396843000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>7106619000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>19107681000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>3488932000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2580789000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2969526000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2551289000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2607965000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>3488932000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2580789000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>2969526000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2551289000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2607965000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>4217781000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>9033597000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>16704432000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>21912176000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>7139835000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>628110000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>624825000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>644247000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>609840000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>639835000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>3589671000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>8408772000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>16060185000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>21302336000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n">
+        <v>14778336000</v>
+      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n">
+        <v>13786620000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3589671000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>8408772000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>16060185000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>6524000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>6500000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>45060859000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>50808878000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>41204984000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>78822630000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>44017885000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>45060859000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>50808878000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>41204984000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>78822630000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>44017885000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>30821327000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>36127725000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>31859767000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>31366042000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>30483389000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dividends Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n">
+        <v>35787598000</v>
+      </c>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>5166548000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>5511325000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1307320000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3130838000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>4261172000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>9072984000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>9169828000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>8037897000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>8538152000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>9273324000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>599931908000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>567274863000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>555395422000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>548143566000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>572962283000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>383491639000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>362491605000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>362541745000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>352968678000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>380639197000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>3822447000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3897409000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>3799540000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>4386267000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>4427663000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>1704119000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>1643661000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1763650000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1660450000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2004411000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>9697361000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>8575316000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>5299458000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>5348605000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>5389623000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>9697361000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8575316000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>5299458000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>5348605000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>5389623000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>86811626000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>63598795000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>72264216000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>68971734000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>71407270000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>30742915000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>26729703000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>27607104000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>27279688000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>29008194000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>10767558000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>9144308000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>10532535000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>10525434000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>11233876000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Financial Assets Designatedas Fair Value Through Profitor Loss Total</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>19975357000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>17585395000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>17074569000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>16754254000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>17774318000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>56068711000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>36869092000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>44657112000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>41692046000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>42399076000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>4459819000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>4742876000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>4456272000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>3761954000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>3909747000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>4432640000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4715697000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>4448658000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>3754340000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>3902133000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>27179000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>27179000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>7614000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>7614000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>7614000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>276996267000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>280033548000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>274958609000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>268839668000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>293500483000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>-1040425460000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>-1019181980000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>-994571589000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-970819586000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>-990888170000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1317421727000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1299215528000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1269530198000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1239659254000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1284388653000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>68967000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>68090000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>67003000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>65056000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>71733000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>27810790000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>28128782000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>24502060000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>27766089000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>45105078000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>1951929000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1978747000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2002086000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1851965000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2121437000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1209133440000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1191750908000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1167093017000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1138254354000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1160307818000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>71053092000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>69953814000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>68563468000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>64471743000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>69123968000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>7403509000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>7335187000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>7302564000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>7250047000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>7658619000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>216440269000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>204783258000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>192853677000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>195174888000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>192323086000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>666075000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>3500450000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>1020965000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>898149000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>32124000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>796000000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>1186000000</v>
+      </c>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n">
+        <v>853000000</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>584000000</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>2973533000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>3496213000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>2975869000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2267623000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2071232000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>38645404000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>37228383000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>35180506000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>34018188000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>35424924000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>2313042000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>2598516000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1959403000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1384654000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>1197132000</v>
+      </c>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>19374173000</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>18555155000</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>17379060000</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>16617573000</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>16825350000</v>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>16958189000</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>16074712000</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>15842043000</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>16015961000</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>17402442000</v>
+      </c>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>39095481000</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>34503234000</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>34636254000</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>34344834000</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>37072690000</v>
+      </c>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>3405587000</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>3162483000</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>2230615000</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1927857000</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2186254000</v>
+      </c>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Duefrom Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>899797000</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>502149000</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>602200000</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>639655000</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>411775000</v>
+      </c>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>86778000</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>66443000</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>160884000</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>37219000</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>85811000</v>
+      </c>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Notes Receivable</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>34703319000</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>30772159000</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>31642555000</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>31740103000</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>34388850000</v>
+      </c>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>-8462000</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>-8345000</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>-8100000</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-7787000</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>-8822000</v>
+      </c>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>34711781000</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>30780504000</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>31650655000</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>31747890000</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>34397672000</v>
+      </c>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>134263776000</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>128365191000</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>119040083000</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>123646094000</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>116869116000</v>
+      </c>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>25245185000</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>17705139000</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>14822701000</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>11652326000</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>10515359000</v>
+      </c>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>109018591000</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>110660052000</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>104217382000</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>111993768000</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>106353757000</v>
+      </c>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>81855210000</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>85634007000</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>73588646000</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>66765565000</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>75759264000</v>
+      </c>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>27163381000</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>25026045000</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>30628736000</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>45228203000</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>30594493000</v>
+      </c>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6636,7 +9428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8268,7 +11060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8296,12 +11088,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>'Net Debt' not found in statements — left blank</t>
         </is>
       </c>
     </row>
